--- a/.claude/skills/weekly_hours_report/scripts/cache/sheet-Jul-2026.xlsx
+++ b/.claude/skills/weekly_hours_report/scripts/cache/sheet-Jul-2026.xlsx
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4751,6 +4751,11 @@
       <c r="F62" t="inlineStr">
         <is>
           <t>ML</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>PTO(PA)</t>
         </is>
       </c>
     </row>
